--- a/src/test/resources/DataTest/Login.xlsx
+++ b/src/test/resources/DataTest/Login.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>Email</t>
   </si>
@@ -22,19 +23,31 @@
     <t>Password</t>
   </si>
   <si>
+    <t>admin@example.com</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>user1@example.com</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>user2@example.com</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t>admin1@example.com</t>
+  </si>
+  <si>
     <t>SessionName</t>
   </si>
   <si>
     <t>SessionValue</t>
-  </si>
-  <si>
-    <t>admin@example.com</t>
-  </si>
-  <si>
-    <t>sp_session</t>
-  </si>
-  <si>
-    <t>2e52bcd0c95f37304c0fb70e2b1144e2f29aa020</t>
   </si>
 </sst>
 </file>
@@ -42,12 +55,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -65,24 +78,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -94,7 +99,51 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -102,40 +151,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -147,67 +167,53 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -216,31 +222,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -252,31 +390,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -288,120 +402,9 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill/>
     </fill>
   </fills>
   <borders count="9">
@@ -417,7 +420,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -425,23 +428,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -476,6 +464,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -493,15 +505,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -513,160 +516,156 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -986,48 +985,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="1" outlineLevelCol="3"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="21.7272727272727"/>
-    <col min="2" max="2" customWidth="true" width="13.7272727272727"/>
-    <col min="3" max="3" customWidth="true" width="12.8181818181818"/>
-    <col min="4" max="4" customWidth="true" width="12.5454545454545"/>
+    <col min="1" max="1" width="21.7272727272727" customWidth="1"/>
+    <col min="2" max="2" width="13.7272727272727" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s" s="0">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="0">
-        <v>123456</v>
-      </c>
-      <c r="C2" t="s" s="2">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s" s="3">
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="admin@example.com"/>
+    <hyperlink ref="A3" r:id="rId2" display="user1@example.com"/>
+    <hyperlink ref="A4" r:id="rId3" display="user2@example.com"/>
+    <hyperlink ref="A5" r:id="rId4" display="admin1@example.com" tooltip="mailto:admin1@example.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>